--- a/extract/test/Resources/sample.xlsx
+++ b/extract/test/Resources/sample.xlsx
@@ -1,34 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miyako/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdal\Dropbox\DailyWorkBU\_blognewsquestions\20250130_sampledata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{358EE738-2B10-6F48-8729-0246CB09987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D78E442-8993-4FB5-9786-8084F3DDA8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16440" xr2:uid="{73ED0379-CA78-724F-B2BF-4DA67EE7A93C}"/>
+    <workbookView xWindow="1920" yWindow="885" windowWidth="24885" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="8" r:id="rId1"/>
+    <sheet name="SalesOrders" sheetId="1" r:id="rId2"/>
+    <sheet name="MyLinks" sheetId="12" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,28 +32,241 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>abcde</t>
-  </si>
-  <si>
-    <t>あいうえお</t>
-  </si>
-  <si>
-    <t>äüöèàù</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="59">
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Rep</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Gill</t>
+  </si>
+  <si>
+    <t>Jardine</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>Kivell</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Howard</t>
+  </si>
+  <si>
+    <t>Morgan</t>
+  </si>
+  <si>
+    <t>Sorvino</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
+    <t>Pencil</t>
+  </si>
+  <si>
+    <t>Binder</t>
+  </si>
+  <si>
+    <t>Pen</t>
+  </si>
+  <si>
+    <t>Andrews</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>Pen Set</t>
+  </si>
+  <si>
+    <t>OrderDate</t>
+  </si>
+  <si>
+    <t>Contextures Recommends</t>
+  </si>
+  <si>
+    <t>Excel Pivot Tables Blog</t>
+  </si>
+  <si>
+    <t>Contextures Excel Blog</t>
+  </si>
+  <si>
+    <t>Contextures Excel Tips Website</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Contextures Sites &amp; News</t>
+  </si>
+  <si>
+    <t>Contextures Excel Newsletter</t>
+  </si>
+  <si>
+    <t>Hundreds of tutorials, tips and sample files</t>
+  </si>
+  <si>
+    <t>Pivot table tutorials and tips, with comments and questions</t>
+  </si>
+  <si>
+    <t>Online Instruction Page</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>•</t>
+  </si>
+  <si>
+    <t>Named Excel Tables</t>
+  </si>
+  <si>
+    <t>Sample Data for Excel</t>
+  </si>
+  <si>
+    <t>The Total column could be changed to a formula, to multiply the Units and Cost columns.</t>
+  </si>
+  <si>
+    <t>Get emails with Excel tips, links, and news</t>
+  </si>
+  <si>
+    <t>Excel tools and training, recommended by Debra</t>
+  </si>
+  <si>
+    <t>Excel Products</t>
+  </si>
+  <si>
+    <t>SalesOrders sheet has office supply sales data for a fictional company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each row represents an order. </t>
+  </si>
+  <si>
+    <t>Excel tutorials and tips, with comments and questions</t>
+  </si>
+  <si>
+    <t>VLOOKUP Function Examples</t>
+  </si>
+  <si>
+    <t>More Sample Data</t>
+  </si>
+  <si>
+    <t>Athletes Sample Data</t>
+  </si>
+  <si>
+    <t>Workplace Safety Sample Data</t>
+  </si>
+  <si>
+    <t>Work Orders Sample Data</t>
+  </si>
+  <si>
+    <t>Insurance Policies Sample Data</t>
+  </si>
+  <si>
+    <t>Food Nutrients Sample Data</t>
+  </si>
+  <si>
+    <t>Food Sales Sample Data</t>
+  </si>
+  <si>
+    <t>Hockey Player Sample Data</t>
+  </si>
+  <si>
+    <t>Related tutorials - for Practice Ideas</t>
+  </si>
+  <si>
+    <t>Excel Drop Down Lists</t>
+  </si>
+  <si>
+    <t>Excel Pivot Tables Intro</t>
+  </si>
+  <si>
+    <t>Excel Formulas and Functions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.00_);\(0.00\)"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF5A8B39"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF974D6E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,7 +277,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,18 +285,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Followed Hyperlink" xfId="3" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="4" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="5" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00_);\(0.00\)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00_);\(0.00\)"/>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -99,10 +390,82 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1076801</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>89380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="A black background with red and blue lights&#10;&#10;Description automatically generated">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B064ECEE-B190-40C1-B51D-8A988F1054BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="85725" y="95250"/>
+          <a:ext cx="1972151" cy="327505"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G44" totalsRowShown="0">
+  <autoFilter ref="A1:G44" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="OrderDate" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Region"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Rep"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Item"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Units"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Unit Cost" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Total" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -110,39 +473,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -194,7 +557,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -246,7 +609,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -305,6 +668,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -313,13 +683,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -384,57 +747,1300 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88555881-27E0-7F4A-B67B-BE4497096FAA}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet30"/>
+  <dimension ref="B1:C27"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="2" max="2" width="2.796875" customWidth="1"/>
+    <col min="3" max="3" width="31.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="2:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:3" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="4"/>
+      <c r="C6" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="B8" s="4"/>
+      <c r="C8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C11" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C12" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C13" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="C20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C22" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C23" s="18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C26" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:C30">
+    <sortCondition ref="C20:C30"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C10" r:id="rId3" xr:uid="{D13F52EB-BE4B-4EFB-B389-A8AC7E2C8260}"/>
+    <hyperlink ref="C21" r:id="rId4" display="https://www.contextures.com/excelsampledataathletes.html" xr:uid="{0335F8CC-FB81-423E-AA69-CCC8801904A0}"/>
+    <hyperlink ref="C27" r:id="rId5" display="https://www.contextures.com/excelsampledatasafety.html" xr:uid="{FFBE4EF0-FA31-4B42-A3CF-7F80A3264010}"/>
+    <hyperlink ref="C26" r:id="rId6" display="https://www.contextures.com/excelsampledataworkorders.html" xr:uid="{3AABA7E2-FFA1-46EE-BF20-3182FF46318A}"/>
+    <hyperlink ref="C25" r:id="rId7" display="https://www.contextures.com/excelsampledatainsurance.html" xr:uid="{B015DCF1-D0A5-45AF-9697-B7E5A09E8890}"/>
+    <hyperlink ref="C22" r:id="rId8" display="https://www.contextures.com/excelsampledatafoodinfo.html" xr:uid="{0EC2F4D8-8571-4781-B615-E0D6577D0C88}"/>
+    <hyperlink ref="C23" r:id="rId9" display="https://www.contextures.com/excelsampledatafoodsales.html" xr:uid="{56728A1E-F6A4-4DD2-93C1-25C689859B93}"/>
+    <hyperlink ref="C24" r:id="rId10" display="https://www.contextures.com/exceldatahockeyplayeranalysis.html" xr:uid="{5A28C4CC-B957-4B35-822B-B22C55FD474D}"/>
+    <hyperlink ref="C11" r:id="rId11" display="https://www.contextures.com/xldataval01.html" xr:uid="{E190C8DE-E8EA-4373-835F-148740E34A46}"/>
+    <hyperlink ref="C12" r:id="rId12" display="https://www.contextures.com/excelpivottablesetup.html" xr:uid="{F9F204F6-CF4E-4BAE-85E5-8685FFD65607}"/>
+    <hyperlink ref="C13" r:id="rId13" display="Formulas and Functions" xr:uid="{95DE3B89-BC29-4747-878A-E25448BBB09E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
+  <drawing r:id="rId15"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.59765625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.69921875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9.09765625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="19">
+        <v>45297</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="13">
+        <v>95</v>
+      </c>
+      <c r="F2" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="G2" s="17">
+        <v>189.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
+        <v>45314</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="13">
+        <v>50</v>
+      </c>
+      <c r="F3" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G3" s="17">
+        <v>999.49999999999989</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>45331</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="13">
+        <v>36</v>
+      </c>
+      <c r="F4" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G4" s="17">
+        <v>179.64000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>45348</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="13">
+        <v>27</v>
+      </c>
+      <c r="F5" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G5" s="17">
+        <v>539.7299999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>45366</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="13">
+        <v>56</v>
+      </c>
+      <c r="F6" s="17">
+        <v>2.99</v>
+      </c>
+      <c r="G6" s="17">
+        <v>167.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>45383</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="13">
+        <v>60</v>
+      </c>
+      <c r="F7" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G7" s="17">
+        <v>299.40000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>45400</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="13">
+        <v>75</v>
+      </c>
+      <c r="F8" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="G8" s="17">
+        <v>149.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>45417</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="13">
+        <v>90</v>
+      </c>
+      <c r="F9" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G9" s="17">
+        <v>449.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>45434</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="13">
+        <v>32</v>
+      </c>
+      <c r="F10" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="G10" s="17">
+        <v>63.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>45451</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="13">
+        <v>60</v>
+      </c>
+      <c r="F11" s="17">
+        <v>8.99</v>
+      </c>
+      <c r="G11" s="17">
+        <v>539.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>45468</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="13">
+        <v>90</v>
+      </c>
+      <c r="F12" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G12" s="17">
+        <v>449.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>45485</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="13">
+        <v>29</v>
+      </c>
+      <c r="F13" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="G13" s="17">
+        <v>57.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>45502</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="13">
+        <v>81</v>
+      </c>
+      <c r="F14" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1619.1899999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>45519</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="13">
+        <v>35</v>
+      </c>
+      <c r="F15" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G15" s="17">
+        <v>174.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>45536</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13">
+        <v>2</v>
+      </c>
+      <c r="F16" s="17">
+        <v>125</v>
+      </c>
+      <c r="G16" s="17">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>45553</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="13">
+        <v>16</v>
+      </c>
+      <c r="F17" s="17">
+        <v>15.99</v>
+      </c>
+      <c r="G17" s="17">
+        <v>255.84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>45570</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="13">
+        <v>28</v>
+      </c>
+      <c r="F18" s="17">
+        <v>8.99</v>
+      </c>
+      <c r="G18" s="17">
+        <v>251.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>45587</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="13">
+        <v>64</v>
+      </c>
+      <c r="F19" s="17">
+        <v>8.99</v>
+      </c>
+      <c r="G19" s="17">
+        <v>575.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="19">
+        <v>45604</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="13">
+        <v>15</v>
+      </c>
+      <c r="F20" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G20" s="17">
+        <v>299.84999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="19">
+        <v>45621</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="13">
+        <v>96</v>
+      </c>
+      <c r="F21" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G21" s="17">
+        <v>479.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="19">
+        <v>45638</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="13">
+        <v>67</v>
+      </c>
+      <c r="F22" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="G22" s="17">
+        <v>86.43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="19">
+        <v>45655</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="13">
+        <v>74</v>
+      </c>
+      <c r="F23" s="17">
+        <v>15.99</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1183.26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A24" s="19">
+        <v>45672</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="13">
+        <v>46</v>
+      </c>
+      <c r="F24" s="17">
+        <v>8.99</v>
+      </c>
+      <c r="G24" s="17">
+        <v>413.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="19">
+        <v>45689</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="13">
+        <v>87</v>
+      </c>
+      <c r="F25" s="17">
+        <v>15</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="19">
+        <v>45706</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="13">
+        <v>4</v>
+      </c>
+      <c r="F26" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G26" s="17">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="19">
+        <v>45723</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="13">
+        <v>7</v>
+      </c>
+      <c r="F27" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G27" s="17">
+        <v>139.92999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="19">
+        <v>45740</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="13">
+        <v>50</v>
+      </c>
+      <c r="F28" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G28" s="17">
+        <v>249.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="19">
+        <v>45757</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="13">
+        <v>66</v>
+      </c>
+      <c r="F29" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="G29" s="17">
+        <v>131.34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A30" s="19">
+        <v>45774</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="13">
+        <v>96</v>
+      </c>
+      <c r="F30" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G30" s="17">
+        <v>479.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A31" s="19">
+        <v>45791</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="13">
+        <v>53</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="G31" s="17">
+        <v>68.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A32" s="19">
+        <v>45808</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="13">
+        <v>80</v>
+      </c>
+      <c r="F32" s="17">
+        <v>8.99</v>
+      </c>
+      <c r="G32" s="17">
+        <v>719.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A33" s="19">
+        <v>45825</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13">
+        <v>5</v>
+      </c>
+      <c r="F33" s="17">
+        <v>125</v>
+      </c>
+      <c r="G33" s="17">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="19">
+        <v>45842</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="13">
+        <v>62</v>
+      </c>
+      <c r="F34" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G34" s="17">
+        <v>309.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="19">
+        <v>45859</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="13">
+        <v>55</v>
+      </c>
+      <c r="F35" s="17">
+        <v>12.49</v>
+      </c>
+      <c r="G35" s="17">
+        <v>686.95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="19">
+        <v>45876</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="13">
+        <v>42</v>
+      </c>
+      <c r="F36" s="17">
+        <v>23.95</v>
+      </c>
+      <c r="G36" s="17">
+        <v>1005.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="19">
+        <v>45893</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="13">
+        <v>3</v>
+      </c>
+      <c r="F37" s="17">
+        <v>275</v>
+      </c>
+      <c r="G37" s="17">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="19">
+        <v>45910</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="13">
+        <v>7</v>
+      </c>
+      <c r="F38" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="G38" s="17">
+        <v>9.0300000000000011</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="19">
+        <v>45927</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="13">
+        <v>76</v>
+      </c>
+      <c r="F39" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="G39" s="17">
+        <v>151.24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="19">
+        <v>45944</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="13">
+        <v>57</v>
+      </c>
+      <c r="F40" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G40" s="17">
+        <v>1139.4299999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="19">
+        <v>45961</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="13">
+        <v>14</v>
+      </c>
+      <c r="F41" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="G41" s="17">
+        <v>18.060000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="19">
+        <v>45978</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="13">
+        <v>11</v>
+      </c>
+      <c r="F42" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G42" s="17">
+        <v>54.89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="19">
+        <v>45995</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="13">
+        <v>94</v>
+      </c>
+      <c r="F43" s="17">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="G43" s="17">
+        <v>1879.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="19">
+        <v>46012</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="13">
+        <v>28</v>
+      </c>
+      <c r="F44" s="17">
+        <v>4.99</v>
+      </c>
+      <c r="G44" s="17">
+        <v>139.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LDeveloped by Contextures Inc.&amp;Cwww.contextures.com&amp;R&amp;D</oddFooter>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E94AE46-A95C-4F85-A614-A6B5CE0429E8}">
+  <sheetPr codeName="Sheet16"/>
+  <dimension ref="A2:C9"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="2" max="2" width="28.19921875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="64" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="B2" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="15"/>
+    </row>
+    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{83B5AB0A-AB0E-42B8-867D-6249A5617347}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{78C7325F-6CC9-4A39-8392-E4674D08A383}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{68C90B41-C893-414D-B7CB-2B4C70813C01}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{69CCE8FB-A633-4769-A1C6-E98799AFDF1F}"/>
+    <hyperlink ref="B9" r:id="rId5" tooltip="Contextures Recommends" xr:uid="{D9F8881F-4EA7-4521-BEA6-D07FED0374F8}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;Lwww.contextures.com&amp;R&amp;D</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<Structure xmlns="thqs">{"Id":"00000000-0000-0000-0000-000000000000","ParentId":null,"Name":"Root","IsExpanded":false,"Children":[]}</Structure>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A901E35E-065E-4A2A-895E-508E746953CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="thqs"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>